--- a/Honda_Logi/Excel_Format/見積書(汎用機種).xlsx
+++ b/Honda_Logi/Excel_Format/見積書(汎用機種).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_hida_data\78_Honda_ロジ\01_PG\git\Honda_Logi\Excel_Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38E9D03-6D0E-4784-AF8E-A6A9C7B6951A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF242188-4DAC-413F-A6E6-9E9ECD32CBEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{7C849D10-9A92-4A04-B2AC-2732B7F77C69}"/>
+    <workbookView xWindow="28680" yWindow="1965" windowWidth="25440" windowHeight="15390" xr2:uid="{7C849D10-9A92-4A04-B2AC-2732B7F77C69}"/>
   </bookViews>
   <sheets>
     <sheet name="見積書(機種)" sheetId="1" r:id="rId1"/>
@@ -177,9 +177,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="180" formatCode="0_);[Red]\(0\)"/>
-  </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -339,7 +336,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -382,49 +379,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="40" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="40" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -806,11 +776,12 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="11.125" style="21" customWidth="1"/>
-    <col min="3" max="9" width="11.125" style="18" customWidth="1"/>
-    <col min="10" max="14" width="11.125" style="28" customWidth="1"/>
-    <col min="15" max="17" width="11.125" style="25" customWidth="1"/>
-    <col min="18" max="18" width="9" style="25"/>
+    <col min="2" max="6" width="11.125" style="14" customWidth="1"/>
+    <col min="7" max="8" width="11.125" style="16" customWidth="1"/>
+    <col min="9" max="9" width="11.125" style="14" customWidth="1"/>
+    <col min="10" max="14" width="11.125" style="17" customWidth="1"/>
+    <col min="15" max="17" width="11.125" style="19" customWidth="1"/>
+    <col min="18" max="18" width="9" style="19"/>
     <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -932,23 +903,10 @@
       <c r="Y4" s="11"/>
     </row>
     <row r="5" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B5" s="19"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
       <c r="I5" s="15"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="O5" s="18"/>
       <c r="T5" s="9"/>
       <c r="U5" s="10"/>
       <c r="V5" s="11"/>
@@ -957,23 +915,10 @@
       <c r="Y5" s="11"/>
     </row>
     <row r="6" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B6" s="19"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
       <c r="E6" s="15"/>
       <c r="F6" s="15"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
       <c r="I6" s="15"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="O6" s="18"/>
       <c r="T6" s="9"/>
       <c r="U6" s="10"/>
       <c r="V6" s="11"/>
@@ -982,23 +927,10 @@
       <c r="Y6" s="11"/>
     </row>
     <row r="7" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B7" s="19"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
       <c r="E7" s="15"/>
       <c r="F7" s="15"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
       <c r="I7" s="15"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="O7" s="18"/>
       <c r="T7" s="9"/>
       <c r="U7" s="10"/>
       <c r="V7" s="11"/>
@@ -1007,23 +939,10 @@
       <c r="Y7" s="11"/>
     </row>
     <row r="8" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B8" s="19"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
       <c r="I8" s="15"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="O8" s="18"/>
       <c r="T8" s="9"/>
       <c r="U8" s="10"/>
       <c r="V8" s="11"/>
@@ -1032,23 +951,10 @@
       <c r="Y8" s="11"/>
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B9" s="19"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="O9" s="18"/>
       <c r="T9" s="9"/>
       <c r="U9" s="10"/>
       <c r="V9" s="11"/>
@@ -1057,23 +963,10 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B10" s="19"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
       <c r="I10" s="15"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="O10" s="18"/>
       <c r="T10" s="9"/>
       <c r="U10" s="10"/>
       <c r="V10" s="11"/>
@@ -1082,23 +975,10 @@
       <c r="Y10" s="11"/>
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B11" s="19"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
       <c r="E11" s="15"/>
       <c r="F11" s="15"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
       <c r="I11" s="15"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="O11" s="18"/>
       <c r="T11" s="9"/>
       <c r="U11" s="10"/>
       <c r="V11" s="11"/>
@@ -1107,23 +987,10 @@
       <c r="Y11" s="11"/>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B12" s="19"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
       <c r="I12" s="15"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="O12" s="18"/>
       <c r="T12" s="9"/>
       <c r="U12" s="10"/>
       <c r="V12" s="11"/>
@@ -1132,23 +999,10 @@
       <c r="Y12" s="11"/>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B13" s="19"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
       <c r="I13" s="15"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="O13" s="18"/>
       <c r="T13" s="9"/>
       <c r="U13" s="12"/>
       <c r="V13" s="11"/>
@@ -1157,23 +1011,9 @@
       <c r="Y13" s="11"/>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B14" s="20"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="I14" s="15"/>
       <c r="S14" s="10"/>
       <c r="T14" s="9"/>
       <c r="U14" s="10"/>
@@ -1183,23 +1023,9 @@
       <c r="Y14" s="11"/>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B15" s="20"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="27"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="I15" s="15"/>
       <c r="T15" s="9"/>
       <c r="U15" s="10"/>
       <c r="V15" s="11"/>
@@ -1208,23 +1034,9 @@
       <c r="Y15" s="11"/>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B16" s="20"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="27"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="I16" s="15"/>
       <c r="T16" s="9"/>
       <c r="U16" s="10"/>
       <c r="V16" s="11"/>
@@ -1232,24 +1044,10 @@
       <c r="X16" s="11"/>
       <c r="Y16" s="11"/>
     </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B17" s="20"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="27"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
+    <row r="17" spans="5:25" x14ac:dyDescent="0.4">
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="I17" s="15"/>
       <c r="T17" s="9"/>
       <c r="U17" s="10"/>
       <c r="V17" s="11"/>
@@ -1257,24 +1055,10 @@
       <c r="X17" s="11"/>
       <c r="Y17" s="11"/>
     </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B18" s="20"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="27"/>
-      <c r="M18" s="27"/>
-      <c r="N18" s="27"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
+    <row r="18" spans="5:25" x14ac:dyDescent="0.4">
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="I18" s="15"/>
       <c r="T18" s="9"/>
       <c r="U18" s="10"/>
       <c r="V18" s="11"/>
@@ -1282,24 +1066,10 @@
       <c r="X18" s="11"/>
       <c r="Y18" s="11"/>
     </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B19" s="20"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="27"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="27"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
+    <row r="19" spans="5:25" x14ac:dyDescent="0.4">
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="I19" s="15"/>
       <c r="T19" s="9"/>
       <c r="U19" s="10"/>
       <c r="V19" s="11"/>
@@ -1307,24 +1077,10 @@
       <c r="X19" s="11"/>
       <c r="Y19" s="11"/>
     </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B20" s="20"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
+    <row r="20" spans="5:25" x14ac:dyDescent="0.4">
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="I20" s="15"/>
       <c r="T20" s="9"/>
       <c r="U20" s="11"/>
       <c r="V20" s="11"/>
@@ -1332,24 +1088,7 @@
       <c r="X20" s="11"/>
       <c r="Y20" s="11"/>
     </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.4">
-      <c r="B21" s="19"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="27"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
+    <row r="21" spans="5:25" x14ac:dyDescent="0.4">
       <c r="T21" s="13"/>
       <c r="U21" s="11"/>
       <c r="V21" s="11"/>
@@ -1357,7 +1096,7 @@
       <c r="X21" s="11"/>
       <c r="Y21" s="11"/>
     </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="22" spans="5:25" x14ac:dyDescent="0.4">
       <c r="T22" s="13"/>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
@@ -1365,7 +1104,7 @@
       <c r="X22" s="11"/>
       <c r="Y22" s="11"/>
     </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="23" spans="5:25" x14ac:dyDescent="0.4">
       <c r="T23" s="11"/>
       <c r="U23" s="11"/>
       <c r="V23" s="11"/>
